--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ113"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98358</v>
+        <v>98361</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13382,6 +13382,116 @@
       <c r="AZ113" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>135993731</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6331699</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ramaria aff. rubrievanescens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>s.auct.scand.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -13499,6 +13609,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93427</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98362</v>
+        <v>98367</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98369</v>
+        <v>98375</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98377</v>
+        <v>98378</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93434</v>
+        <v>93440</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98378</v>
+        <v>98384</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93440</v>
+        <v>93444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98384</v>
+        <v>98388</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98388</v>
+        <v>98390</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98390</v>
+        <v>98392</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93446</v>
+        <v>93459</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98392</v>
+        <v>98405</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98405</v>
+        <v>98407</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
         <v>136663268</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136663275</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136663261</v>
       </c>
       <c r="B29" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>136663302</v>
       </c>
       <c r="B30" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>136663278</v>
       </c>
       <c r="B38" t="n">
-        <v>93460</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>136663279</v>
       </c>
       <c r="B43" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136663322</v>
       </c>
       <c r="B44" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>136663270</v>
       </c>
       <c r="B58" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>136663304</v>
       </c>
       <c r="B59" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>136663312</v>
       </c>
       <c r="B60" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>136663316</v>
       </c>
       <c r="B61" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136663321</v>
       </c>
       <c r="B62" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>136663263</v>
       </c>
       <c r="B66" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>136663289</v>
       </c>
       <c r="B67" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>136663252</v>
       </c>
       <c r="B69" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136663307</v>
       </c>
       <c r="B70" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136663309</v>
       </c>
       <c r="B71" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>136663260</v>
       </c>
       <c r="B92" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>136663285</v>
       </c>
       <c r="B93" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>136663247</v>
       </c>
       <c r="B97" t="n">
-        <v>98407</v>
+        <v>98410</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136663246</v>
       </c>
       <c r="B99" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>136663262</v>
       </c>
       <c r="B100" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>136663276</v>
       </c>
       <c r="B101" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>136663298</v>
       </c>
       <c r="B102" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136663317</v>
       </c>
       <c r="B103" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136663320</v>
       </c>
       <c r="B104" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136663329</v>
       </c>
       <c r="B105" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137389228</v>
       </c>
       <c r="B3" t="n">
-        <v>87423</v>
+        <v>87428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137389220</v>
       </c>
       <c r="B47" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137389223</v>
       </c>
       <c r="B48" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137389219</v>
       </c>
       <c r="B66" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>137389224</v>
       </c>
       <c r="B67" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>137389221</v>
       </c>
       <c r="B77" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>137389222</v>
       </c>
       <c r="B78" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137389225</v>
       </c>
       <c r="B79" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>137389226</v>
       </c>
       <c r="B80" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>137389227</v>
       </c>
       <c r="B81" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>137389270</v>
       </c>
       <c r="B102" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137389228</v>
       </c>
       <c r="B3" t="n">
-        <v>87428</v>
+        <v>87439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137389220</v>
       </c>
       <c r="B47" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137389223</v>
       </c>
       <c r="B48" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137389219</v>
       </c>
       <c r="B66" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>137389224</v>
       </c>
       <c r="B67" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>137389221</v>
       </c>
       <c r="B77" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>137389222</v>
       </c>
       <c r="B78" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137389225</v>
       </c>
       <c r="B79" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>137389226</v>
       </c>
       <c r="B80" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>137389227</v>
       </c>
       <c r="B81" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137389228</v>
       </c>
       <c r="B3" t="n">
-        <v>87439</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137389220</v>
       </c>
       <c r="B47" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137389223</v>
       </c>
       <c r="B48" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137389219</v>
       </c>
       <c r="B66" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>137389224</v>
       </c>
       <c r="B67" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>137389221</v>
       </c>
       <c r="B77" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>137389222</v>
       </c>
       <c r="B78" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137389225</v>
       </c>
       <c r="B79" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>137389226</v>
       </c>
       <c r="B80" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>137389227</v>
       </c>
       <c r="B81" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137389228</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137389220</v>
       </c>
       <c r="B47" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137389223</v>
       </c>
       <c r="B48" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137389219</v>
       </c>
       <c r="B66" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>137389224</v>
       </c>
       <c r="B67" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>137389221</v>
       </c>
       <c r="B77" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>137389222</v>
       </c>
       <c r="B78" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137389225</v>
       </c>
       <c r="B79" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>137389226</v>
       </c>
       <c r="B80" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>137389227</v>
       </c>
       <c r="B81" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137389228</v>
       </c>
       <c r="B3" t="n">
-        <v>87443</v>
+        <v>87447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137389220</v>
       </c>
       <c r="B47" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137389223</v>
       </c>
       <c r="B48" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137389219</v>
       </c>
       <c r="B66" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>137389224</v>
       </c>
       <c r="B67" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>137389221</v>
       </c>
       <c r="B77" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>137389222</v>
       </c>
       <c r="B78" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137389225</v>
       </c>
       <c r="B79" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>137389226</v>
       </c>
       <c r="B80" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>137389227</v>
       </c>
       <c r="B81" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>137389270</v>
       </c>
       <c r="B102" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
